--- a/backtest_runs/20260410_193731/by_symbol/FECM/FECM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FECM/FECM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-5282.749999999998</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>94717.25</v>
@@ -817,7 +817,7 @@
         <v>-11000.54999999999</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>116966.95</v>
@@ -909,7 +909,7 @@
         <v>-3791.150000000007</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>116780.5</v>
@@ -955,7 +955,7 @@
         <v>-5034.149999999992</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>111746.35</v>
@@ -1001,7 +1001,7 @@
         <v>-497.2000000000004</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>111249.15</v>
@@ -1139,7 +1139,7 @@
         <v>-497.2000000000115</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>121193.15</v>
@@ -1323,7 +1323,7 @@
         <v>-2299.549999999984</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>121006.7</v>
@@ -1415,7 +1415,7 @@
         <v>-3480.400000000014</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>117526.3</v>
@@ -1553,7 +1553,7 @@
         <v>-9384.649999999998</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>116221.15</v>
